--- a/data/trans_camb/P5_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P5_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 33,36</t>
+          <t>-1,95; 30,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 27,63</t>
+          <t>-1,74; 28,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-29,78; -9,56</t>
+          <t>-29,5; -9,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 33,2</t>
+          <t>-0,35; 32,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 29,37</t>
+          <t>-0,22; 29,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,32; -9,28</t>
+          <t>-32,03; -8,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 29,08</t>
+          <t>3,43; 27,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 24,09</t>
+          <t>2,63; 23,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-26,53; -10,86</t>
+          <t>-25,94; -11,92</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 230,82</t>
+          <t>-8,86; 211,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 200,81</t>
+          <t>-10,49; 220,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -60,92</t>
+          <t>-100,0; -57,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 204,99</t>
+          <t>-1,55; 209,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 181,16</t>
+          <t>-3,6; 179,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-96,49; -44,3</t>
+          <t>-95,34; -40,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,79; 165,9</t>
+          <t>12,76; 159,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,94; 144,5</t>
+          <t>9,68; 141,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-95,69; -65,66</t>
+          <t>-94,7; -66,3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 14,97</t>
+          <t>-9,13; 15,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,22; 37,77</t>
+          <t>11,47; 38,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 42,64</t>
+          <t>-13,6; 44,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 20,81</t>
+          <t>-6,61; 20,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,43; 42,05</t>
+          <t>16,95; 40,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,38; -8,68</t>
+          <t>-30,65; -8,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 14,74</t>
+          <t>-4,21; 13,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,27; 36,37</t>
+          <t>18,6; 35,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 20,33</t>
+          <t>-16,78; 25,66</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,35; 80,03</t>
+          <t>-30,63; 81,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,47; 198,56</t>
+          <t>35,94; 216,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,48; 234,58</t>
+          <t>-49,3; 241,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 93,89</t>
+          <t>-19,3; 90,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>47,5; 208,42</t>
+          <t>46,81; 188,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,09; -37,8</t>
+          <t>-81,22; -37,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 65,94</t>
+          <t>-13,26; 59,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>56,96; 160,3</t>
+          <t>58,31; 162,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,79; 90,66</t>
+          <t>-57,86; 109,13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 33,21</t>
+          <t>3,76; 34,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 4,97</t>
+          <t>-20,63; 7,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-23,94; 1,07</t>
+          <t>-23,44; 1,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 27,83</t>
+          <t>0,68; 29,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 10,19</t>
+          <t>-15,13; 9,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 0,62</t>
+          <t>-22,93; 0,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 26,27</t>
+          <t>6,14; 26,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 4,19</t>
+          <t>-14,33; 4,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,84; -2,4</t>
+          <t>-19,76; -2,82</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,31; 124,84</t>
+          <t>9,13; 130,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,16; 18,32</t>
+          <t>-52,62; 31,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-60,59; 3,88</t>
+          <t>-58,01; 8,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 105,87</t>
+          <t>-1,28; 106,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,47; 40,47</t>
+          <t>-39,06; 37,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,95; 3,87</t>
+          <t>-57,92; 4,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,26; 96,17</t>
+          <t>16,41; 90,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,09; 16,06</t>
+          <t>-38,87; 16,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,53; -6,96</t>
+          <t>-53,71; -8,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 21,9</t>
+          <t>-5,16; 21,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 23,33</t>
+          <t>-7,08; 22,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 2,4</t>
+          <t>-19,7; 2,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 14,09</t>
+          <t>-11,17; 14,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 24,63</t>
+          <t>-3,13; 25,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 2,36</t>
+          <t>-20,14; 3,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 14,18</t>
+          <t>-5,74; 13,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 19,59</t>
+          <t>-0,87; 19,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,37; -0,83</t>
+          <t>-17,34; -0,85</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,53; 117,63</t>
+          <t>-19,43; 119,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,0; 119,73</t>
+          <t>-23,05; 115,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-67,63; 14,9</t>
+          <t>-65,55; 16,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-38,24; 76,24</t>
+          <t>-38,21; 78,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 138,08</t>
+          <t>-10,7; 142,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,95; 15,77</t>
+          <t>-71,33; 21,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 72,16</t>
+          <t>-20,38; 68,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,09; 102,68</t>
+          <t>-3,26; 94,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-62,63; -4,37</t>
+          <t>-62,85; -4,24</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-28,88; 36,32</t>
+          <t>-26,08; 34,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-60,45; -3,17</t>
+          <t>-57,65; -0,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-84,09; -33,51</t>
+          <t>-84,86; -32,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 49,29</t>
+          <t>-7,75; 50,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-30,05; 25,51</t>
+          <t>-27,77; 27,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-62,76; -14,39</t>
+          <t>-64,29; -12,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 35,79</t>
+          <t>-6,85; 35,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-35,26; 6,83</t>
+          <t>-34,14; 6,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-66,44; -28,97</t>
+          <t>-65,85; -29,47</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 85,18</t>
+          <t>-33,03; 80,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-72,94; -7,99</t>
+          <t>-71,08; -4,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -84,03</t>
+          <t>-100,0; -82,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 271,81</t>
+          <t>-12,07; 276,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-50,13; 135,04</t>
+          <t>-47,6; 159,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -55,47</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 104,7</t>
+          <t>-9,83; 106,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-54,17; 20,39</t>
+          <t>-53,63; 18,91</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -87,29</t>
+          <t>-100,0; -87,69</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>14,25; 43,95</t>
+          <t>12,71; 44,24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8,63; 42,03</t>
+          <t>6,95; 42,9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 20,34</t>
+          <t>-4,88; 19,68</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23,47; 50,66</t>
+          <t>23,78; 51,53</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,9; 45,57</t>
+          <t>12,14; 46,94</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 12,62</t>
+          <t>-8,52; 11,63</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,78; 42,71</t>
+          <t>22,39; 43,67</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>14,56; 39,29</t>
+          <t>15,04; 38,63</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 12,93</t>
+          <t>-3,97; 12,37</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>59,5; 443,94</t>
+          <t>52,17; 436,41</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>31,91; 411,94</t>
+          <t>26,27; 453,25</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-29,94; 218,02</t>
+          <t>-25,72; 201,3</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>123,83; 721,21</t>
+          <t>120,18; 716,52</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>60,94; 635,71</t>
+          <t>54,92; 599,22</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-46,51; 181,12</t>
+          <t>-50,78; 162,49</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>119,85; 441,52</t>
+          <t>115,56; 433,1</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>78,84; 388,67</t>
+          <t>85,61; 392,13</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-22,25; 137,95</t>
+          <t>-21,35; 130,22</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7,65; 28,47</t>
+          <t>8,54; 28,08</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 19,45</t>
+          <t>-0,6; 17,72</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 17,43</t>
+          <t>-2,49; 17,08</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8,78; 28,29</t>
+          <t>8,4; 28,84</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 19,43</t>
+          <t>0,97; 21,19</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 19,87</t>
+          <t>-0,65; 20,76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,59; 26,15</t>
+          <t>10,48; 25,24</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,43; 16,06</t>
+          <t>2,33; 16,06</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,95; 15,49</t>
+          <t>1,31; 15,86</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>24,16; 122,11</t>
+          <t>26,48; 124,39</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 84,99</t>
+          <t>-2,76; 80,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 77,17</t>
+          <t>-7,73; 75,64</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>24,71; 126,14</t>
+          <t>22,04; 134,87</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 87,79</t>
+          <t>2,78; 96,02</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 88,65</t>
+          <t>-3,06; 96,36</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,86; 110,85</t>
+          <t>33,86; 103,41</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>7,55; 68,35</t>
+          <t>6,88; 67,26</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3,28; 65,34</t>
+          <t>4,15; 66,7</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-21,54; -1,24</t>
+          <t>-23,17; -2,04</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 5,11</t>
+          <t>-15,09; 5,72</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-30,63; -11,52</t>
+          <t>-31,59; -11,27</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-22,6; -3,13</t>
+          <t>-23,05; -3,13</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-19,72; -0,17</t>
+          <t>-18,48; 0,91</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-33,22; -15,13</t>
+          <t>-32,8; -14,01</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-19,84; -5,66</t>
+          <t>-20,04; -5,73</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-14,81; -0,91</t>
+          <t>-14,57; 0,75</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-29,6; -15,88</t>
+          <t>-29,71; -16,13</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-51,84; -3,53</t>
+          <t>-54,69; -5,97</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 17,6</t>
+          <t>-36,29; 21,19</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-73,65; -38,69</t>
+          <t>-74,1; -38,19</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-51,79; -9,35</t>
+          <t>-53,71; -9,2</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-43,85; -0,3</t>
+          <t>-43,47; 2,45</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-75,31; -46,32</t>
+          <t>-74,69; -43,67</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-47,8; -16,57</t>
+          <t>-48,3; -16,75</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-35,73; -2,65</t>
+          <t>-35,39; 2,95</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-70,76; -47,04</t>
+          <t>-70,65; -47,63</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>4,77; 15,16</t>
+          <t>5,33; 14,83</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,59; 11,98</t>
+          <t>2,16; 11,33</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 3,41</t>
+          <t>-12,01; 3,93</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5,53; 14,66</t>
+          <t>5,97; 15,08</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>4,85; 14,0</t>
+          <t>4,84; 14,03</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-15,08; -7,06</t>
+          <t>-14,63; -6,85</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,89; 13,26</t>
+          <t>7,16; 13,57</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>5,0; 11,5</t>
+          <t>5,08; 11,51</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-12,34; -2,76</t>
+          <t>-12,06; -4,0</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>15,67; 59,94</t>
+          <t>17,53; 56,42</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>7,85; 46,3</t>
+          <t>6,97; 43,22</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-41,54; 14,36</t>
+          <t>-41,05; 18,05</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>17,91; 57,26</t>
+          <t>19,69; 58,15</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>15,63; 55,17</t>
+          <t>15,97; 56,1</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-49,57; -26,22</t>
+          <t>-48,83; -26,66</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>22,88; 49,8</t>
+          <t>24,1; 51,63</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>16,61; 43,42</t>
+          <t>17,33; 43,63</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-41,93; -8,34</t>
+          <t>-41,32; -14,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P5_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 30,15</t>
+          <t>-1,58; 32,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 28,72</t>
+          <t>-1,68; 26,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-29,5; -9,99</t>
+          <t>-29,53; -9,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 32,65</t>
+          <t>-1,48; 32,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 29,27</t>
+          <t>-0,09; 28,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,03; -8,6</t>
+          <t>-31,14; -9,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 27,07</t>
+          <t>4,64; 28,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 23,65</t>
+          <t>2,28; 22,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-25,94; -11,92</t>
+          <t>-26,81; -12,18</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 211,16</t>
+          <t>-7,9; 228,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 220,62</t>
+          <t>-5,58; 212,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -57,23</t>
+          <t>-100,0; -64,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 209,95</t>
+          <t>-6,25; 190,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 179,15</t>
+          <t>-1,65; 167,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,34; -40,14</t>
+          <t>-95,16; -39,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,76; 159,86</t>
+          <t>16,58; 162,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,68; 141,34</t>
+          <t>10,39; 128,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-94,7; -66,3</t>
+          <t>-95,28; -68,18</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 15,77</t>
+          <t>-8,42; 15,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,47; 38,33</t>
+          <t>12,51; 37,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 44,13</t>
+          <t>-12,81; 40,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 20,15</t>
+          <t>-6,31; 20,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,95; 40,99</t>
+          <t>16,44; 41,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,65; -8,81</t>
+          <t>-29,85; -8,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 13,85</t>
+          <t>-2,83; 14,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,6; 35,96</t>
+          <t>18,65; 36,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 25,66</t>
+          <t>-16,97; 20,64</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,63; 81,99</t>
+          <t>-28,6; 83,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,94; 216,63</t>
+          <t>38,53; 193,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,3; 241,62</t>
+          <t>-47,16; 251,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 90,13</t>
+          <t>-18,28; 87,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>46,81; 188,12</t>
+          <t>44,43; 184,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,22; -37,71</t>
+          <t>-80,04; -36,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 59,19</t>
+          <t>-10,01; 64,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,31; 162,67</t>
+          <t>59,46; 169,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-57,86; 109,13</t>
+          <t>-58,82; 83,79</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 34,08</t>
+          <t>2,52; 33,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 7,56</t>
+          <t>-21,31; 6,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-23,44; 1,27</t>
+          <t>-24,51; 1,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 29,15</t>
+          <t>0,56; 28,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 9,98</t>
+          <t>-15,56; 10,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 0,69</t>
+          <t>-23,01; 1,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 26,17</t>
+          <t>6,31; 26,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 4,61</t>
+          <t>-14,87; 4,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,76; -2,82</t>
+          <t>-20,49; -3,17</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,13; 130,08</t>
+          <t>5,59; 126,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,62; 31,12</t>
+          <t>-53,23; 26,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,01; 8,76</t>
+          <t>-61,45; 3,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 106,82</t>
+          <t>1,55; 108,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,06; 37,95</t>
+          <t>-40,36; 40,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,92; 4,82</t>
+          <t>-58,87; 6,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,41; 90,89</t>
+          <t>15,54; 87,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-38,87; 16,74</t>
+          <t>-39,57; 17,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,71; -8,95</t>
+          <t>-54,4; -10,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 21,98</t>
+          <t>-7,53; 19,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 22,56</t>
+          <t>-7,06; 21,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 2,66</t>
+          <t>-20,17; 2,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 14,04</t>
+          <t>-10,16; 15,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 25,21</t>
+          <t>-3,88; 23,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 3,95</t>
+          <t>-21,14; 2,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 13,38</t>
+          <t>-5,34; 14,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 19,46</t>
+          <t>-0,73; 18,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,34; -0,85</t>
+          <t>-16,8; -0,72</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 119,17</t>
+          <t>-25,97; 109,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 115,79</t>
+          <t>-24,44; 116,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,55; 16,05</t>
+          <t>-68,04; 16,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-38,21; 78,89</t>
+          <t>-35,35; 86,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 142,63</t>
+          <t>-14,9; 133,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-71,33; 21,54</t>
+          <t>-76,08; 12,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 68,31</t>
+          <t>-21,27; 71,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 94,97</t>
+          <t>-2,94; 94,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-62,85; -4,24</t>
+          <t>-63,74; -3,72</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-26,08; 34,39</t>
+          <t>-25,03; 36,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-57,65; -0,72</t>
+          <t>-58,51; -1,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-84,86; -32,94</t>
+          <t>-83,65; -34,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 50,65</t>
+          <t>-7,69; 49,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-27,77; 27,72</t>
+          <t>-26,4; 27,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-64,29; -12,67</t>
+          <t>-62,87; -12,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 35,49</t>
+          <t>-10,22; 34,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-34,14; 6,24</t>
+          <t>-34,23; 6,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-65,85; -29,47</t>
+          <t>-66,87; -31,07</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,03; 80,74</t>
+          <t>-30,98; 91,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-71,08; -4,33</t>
+          <t>-71,21; -4,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -82,35</t>
+          <t>-100,0; -82,71</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 276,69</t>
+          <t>-13,36; 287,87</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-47,6; 159,35</t>
+          <t>-45,51; 150,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -55,47</t>
+          <t>-100,0; -62,96</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 106,83</t>
+          <t>-13,23; 104,92</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-53,63; 18,91</t>
+          <t>-53,68; 20,68</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -87,69</t>
+          <t>-100,0; -88,65</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>12,71; 44,24</t>
+          <t>12,28; 40,65</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6,95; 42,9</t>
+          <t>6,29; 42,43</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 19,68</t>
+          <t>-5,41; 20,2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23,78; 51,53</t>
+          <t>23,81; 51,27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,14; 46,94</t>
+          <t>11,53; 45,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 11,63</t>
+          <t>-7,61; 12,05</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,39; 43,67</t>
+          <t>23,34; 43,65</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>15,04; 38,63</t>
+          <t>14,51; 38,53</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 12,37</t>
+          <t>-3,49; 12,88</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>52,17; 436,41</t>
+          <t>47,63; 386,96</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>26,27; 453,25</t>
+          <t>20,49; 430,15</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-25,72; 201,3</t>
+          <t>-30,76; 205,87</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>120,18; 716,52</t>
+          <t>129,9; 703,44</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>54,92; 599,22</t>
+          <t>63,61; 654,96</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-50,78; 162,49</t>
+          <t>-47,45; 170,5</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>115,56; 433,1</t>
+          <t>113,2; 415,21</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>85,61; 392,13</t>
+          <t>75,32; 365,49</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 130,22</t>
+          <t>-22,26; 118,58</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>8,54; 28,08</t>
+          <t>7,97; 27,85</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 17,72</t>
+          <t>-2,12; 18,45</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 17,08</t>
+          <t>-3,52; 16,76</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8,4; 28,84</t>
+          <t>8,65; 28,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,97; 21,19</t>
+          <t>0,54; 20,2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 20,76</t>
+          <t>-0,35; 20,49</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,48; 25,24</t>
+          <t>11,46; 25,5</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,33; 16,06</t>
+          <t>2,66; 16,46</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,31; 15,86</t>
+          <t>1,02; 16,98</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>26,48; 124,39</t>
+          <t>21,98; 121,8</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 80,71</t>
+          <t>-7,22; 79,61</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 75,64</t>
+          <t>-10,97; 71,84</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22,04; 134,87</t>
+          <t>25,33; 127,76</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,78; 96,02</t>
+          <t>0,19; 94,96</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 96,36</t>
+          <t>-1,15; 89,1</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,86; 103,41</t>
+          <t>36,8; 111,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>6,88; 67,26</t>
+          <t>8,58; 70,15</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4,15; 66,7</t>
+          <t>3,16; 72,73</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-23,17; -2,04</t>
+          <t>-22,96; -1,55</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 5,72</t>
+          <t>-15,56; 5,1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-31,59; -11,27</t>
+          <t>-30,83; -11,1</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-23,05; -3,13</t>
+          <t>-23,94; -3,79</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 0,91</t>
+          <t>-19,62; 0,12</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-32,8; -14,01</t>
+          <t>-33,07; -14,76</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-20,04; -5,73</t>
+          <t>-20,55; -6,17</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 0,75</t>
+          <t>-14,63; -0,33</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-29,71; -16,13</t>
+          <t>-28,96; -16,13</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-54,69; -5,97</t>
+          <t>-53,37; -1,14</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-36,29; 21,19</t>
+          <t>-36,91; 18,09</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-74,1; -38,19</t>
+          <t>-73,39; -37,25</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-53,71; -9,2</t>
+          <t>-53,59; -11,45</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-43,47; 2,45</t>
+          <t>-44,0; 0,61</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-74,69; -43,67</t>
+          <t>-75,69; -43,65</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-48,3; -16,75</t>
+          <t>-49,56; -17,86</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-35,39; 2,95</t>
+          <t>-34,82; -0,38</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-70,65; -47,63</t>
+          <t>-70,71; -47,73</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>5,33; 14,83</t>
+          <t>5,19; 15,21</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,16; 11,33</t>
+          <t>1,97; 11,23</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 3,93</t>
+          <t>-12,15; 3,72</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5,97; 15,08</t>
+          <t>5,91; 14,63</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>4,84; 14,03</t>
+          <t>5,17; 14,24</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-14,63; -6,85</t>
+          <t>-14,75; -6,74</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,16; 13,57</t>
+          <t>6,82; 13,54</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>5,08; 11,51</t>
+          <t>4,87; 11,43</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -4,0</t>
+          <t>-12,44; -3,56</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>17,53; 56,42</t>
+          <t>17,01; 59,31</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>6,97; 43,22</t>
+          <t>6,6; 44,69</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-41,05; 18,05</t>
+          <t>-41,18; 14,99</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>19,69; 58,15</t>
+          <t>19,92; 57,51</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>15,97; 56,1</t>
+          <t>16,86; 55,33</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-48,83; -26,66</t>
+          <t>-49,41; -26,73</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>24,1; 51,63</t>
+          <t>23,0; 50,72</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>17,33; 43,63</t>
+          <t>16,82; 43,64</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-41,32; -14,38</t>
+          <t>-42,03; -12,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P5_R-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16,73</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14,48</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-19,44</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>14,46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>12,41</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-18,79</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16,73</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,48</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-19,2</t>
+          <t>-18,56</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-19,0</t>
+          <t>-18,99</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 32,53</t>
+          <t>-0,41; 33,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 26,54</t>
+          <t>-0,36; 29,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-29,53; -9,49</t>
+          <t>-31,62; -10,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 32,41</t>
+          <t>-1,07; 33,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 28,26</t>
+          <t>-1,59; 27,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,14; -9,24</t>
+          <t>-29,47; -9,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 28,32</t>
+          <t>4,89; 29,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 22,41</t>
+          <t>3,34; 24,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-26,81; -12,18</t>
+          <t>-26,63; -11,07</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>71,86%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62,19%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-83,51%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>70,42%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>60,44%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-91,49%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71,86%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>62,19%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-82,48%</t>
+          <t>-90,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-86,52%</t>
+          <t>-86,47%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 228,69</t>
+          <t>-1,89; 204,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 212,17</t>
+          <t>-3,1; 181,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -64,53</t>
+          <t>-96,82; -55,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 190,46</t>
+          <t>-11,15; 230,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 167,59</t>
+          <t>-11,2; 200,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,16; -39,98</t>
+          <t>-100,0; -52,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,58; 162,7</t>
+          <t>16,79; 165,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,39; 128,28</t>
+          <t>9,94; 144,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-95,28; -68,18</t>
+          <t>-95,35; -67,58</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,05</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29,42</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-19,19</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>25,05</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8,33</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,05</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>29,42</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-19,03</t>
+          <t>-6,8</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,3</t>
+          <t>-13,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 15,92</t>
+          <t>-6,37; 20,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,51; 37,3</t>
+          <t>16,43; 42,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 40,92</t>
+          <t>-29,57; -8,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 20,45</t>
+          <t>-9,66; 14,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,44; 41,93</t>
+          <t>12,22; 37,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,85; -8,99</t>
+          <t>-17,84; 4,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 14,99</t>
+          <t>-4,08; 14,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,65; 36,43</t>
+          <t>18,27; 36,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 20,64</t>
+          <t>-20,49; -6,17</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23,86%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-64,96%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>12,34%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>99,74%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>33,15%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23,86%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-64,42%</t>
+          <t>-27,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-19,43%</t>
+          <t>-48,43%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 83,33</t>
+          <t>-20,31; 93,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,53; 193,89</t>
+          <t>47,5; 208,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,16; 251,37</t>
+          <t>-79,25; -36,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 87,02</t>
+          <t>-31,35; 80,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,43; 184,3</t>
+          <t>37,47; 198,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-80,04; -36,06</t>
+          <t>-58,24; 28,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 64,2</t>
+          <t>-12,26; 65,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,46; 169,52</t>
+          <t>56,96; 160,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,82; 83,79</t>
+          <t>-65,85; -25,64</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14,79</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,6</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-11,27</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>18,71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-7,59</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-11,38</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14,79</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,6</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-11,12</t>
+          <t>-12,02</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-11,27</t>
+          <t>-11,63</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,52; 33,07</t>
+          <t>1,06; 27,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,31; 6,79</t>
+          <t>-15,47; 10,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 1,19</t>
+          <t>-23,04; 0,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 28,65</t>
+          <t>4,26; 33,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 10,24</t>
+          <t>-21,9; 4,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 1,29</t>
+          <t>-24,8; 0,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 26,36</t>
+          <t>6,03; 26,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 4,76</t>
+          <t>-14,14; 4,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-20,49; -3,17</t>
+          <t>-19,98; -2,85</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>45,71%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-8,04%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-34,82%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>55,88%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-22,65%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-33,99%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>45,71%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-8,04%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-34,36%</t>
+          <t>-35,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-34,24%</t>
+          <t>-35,35%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,59; 126,21</t>
+          <t>1,38; 105,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-53,23; 26,27</t>
+          <t>-42,47; 40,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,45; 3,73</t>
+          <t>-61,82; 2,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 108,65</t>
+          <t>10,31; 124,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,36; 40,87</t>
+          <t>-55,16; 18,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,87; 6,52</t>
+          <t>-61,79; 0,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,54; 87,68</t>
+          <t>16,26; 96,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-39,57; 17,8</t>
+          <t>-37,09; 16,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,4; -10,57</t>
+          <t>-53,92; -9,1</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,54</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-8,59</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>7,19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>7,99</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-9,02</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,16</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-9,42</t>
+          <t>-8,93</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-9,23</t>
+          <t>-8,73</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 19,7</t>
+          <t>-11,35; 14,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 21,49</t>
+          <t>-2,49; 24,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 2,99</t>
+          <t>-20,28; 3,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 15,32</t>
+          <t>-6,41; 21,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 23,92</t>
+          <t>-5,3; 23,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 2,33</t>
+          <t>-20,84; 2,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 14,14</t>
+          <t>-5,34; 14,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 18,68</t>
+          <t>-0,31; 19,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,8; -0,72</t>
+          <t>-16,82; 0,03</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>43,53%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-36,78%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>29,59%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>32,89%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-37,11%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>43,53%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-40,33%</t>
+          <t>-36,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-38,77%</t>
+          <t>-36,7%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 109,93</t>
+          <t>-38,24; 76,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 116,08</t>
+          <t>-8,94; 138,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-68,04; 16,72</t>
+          <t>-72,76; 20,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,35; 86,68</t>
+          <t>-22,53; 117,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 133,2</t>
+          <t>-20,0; 119,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-76,08; 12,46</t>
+          <t>-68,14; 17,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,27; 71,94</t>
+          <t>-19,28; 72,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 94,63</t>
+          <t>0,09; 102,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,74; -3,72</t>
+          <t>-61,76; -1,64</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>22,79</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,9</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-37,18</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>4,69</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-32,47</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-61,95</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>22,79</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,9</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-37,24</t>
+          <t>-61,8</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-48,5</t>
+          <t>-48,39</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 36,35</t>
+          <t>-5,8; 49,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-58,51; -1,02</t>
+          <t>-30,05; 25,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-83,65; -34,29</t>
+          <t>-62,73; -14,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 49,4</t>
+          <t>-28,88; 36,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-26,4; 27,32</t>
+          <t>-60,45; -3,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-62,87; -12,12</t>
+          <t>-83,96; -33,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 34,7</t>
+          <t>-7,35; 35,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-34,23; 6,91</t>
+          <t>-35,26; 6,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-66,87; -31,07</t>
+          <t>-66,31; -28,85</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>58,78%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-95,89%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>7,37%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-51,06%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-97,42%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>58,78%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-96,06%</t>
+          <t>-97,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-96,84%</t>
+          <t>-96,63%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 91,19</t>
+          <t>-9,74; 271,81</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-71,21; -4,45</t>
+          <t>-50,13; 135,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -82,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 287,87</t>
+          <t>-34,76; 85,18</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-45,51; 150,27</t>
+          <t>-72,94; -7,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -62,96</t>
+          <t>-100,0; -82,66</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 104,92</t>
+          <t>-12,34; 104,7</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-53,68; 20,68</t>
+          <t>-54,17; 20,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -88,65</t>
+          <t>-100,0; -86,54</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>38,05</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>28,25</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>28,65</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>24,68</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>6,77</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>38,05</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>28,25</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,96</t>
+          <t>6,51</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>4,38</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>12,28; 40,65</t>
+          <t>23,47; 50,66</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6,29; 42,43</t>
+          <t>12,9; 45,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 20,2</t>
+          <t>-8,08; 12,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23,81; 51,27</t>
+          <t>14,25; 43,95</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,53; 45,66</t>
+          <t>8,63; 42,03</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 12,05</t>
+          <t>-6,4; 20,3</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,34; 43,65</t>
+          <t>22,78; 42,71</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>14,51; 38,53</t>
+          <t>14,56; 39,29</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 12,88</t>
+          <t>-3,66; 13,57</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>307,51%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>228,3%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>18,62%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>179,5%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>154,61%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>42,44%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>307,51%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>228,3%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>47,63; 386,96</t>
+          <t>123,83; 721,21</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>20,49; 430,15</t>
+          <t>60,94; 635,71</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-30,76; 205,87</t>
+          <t>-46,52; 183,56</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>129,9; 703,44</t>
+          <t>59,5; 443,94</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>63,61; 654,96</t>
+          <t>31,91; 411,94</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-47,45; 170,5</t>
+          <t>-30,57; 213,09</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>113,2; 415,21</t>
+          <t>119,85; 441,52</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>75,32; 365,49</t>
+          <t>78,84; 388,67</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-22,26; 118,58</t>
+          <t>-21,01; 138,41</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>18,45</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10,47</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>11,77</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>18,14</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>8,68</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>7,22</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>18,45</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>10,47</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,08</t>
+          <t>6,97</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,76</t>
+          <t>9,5</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7,97; 27,85</t>
+          <t>8,78; 28,29</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 18,45</t>
+          <t>-0,26; 19,43</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 16,76</t>
+          <t>0,83; 21,35</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8,65; 28,0</t>
+          <t>7,65; 28,47</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,54; 20,2</t>
+          <t>-0,2; 19,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 20,49</t>
+          <t>-3,61; 16,83</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,46; 25,5</t>
+          <t>11,59; 26,15</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,66; 16,46</t>
+          <t>2,43; 16,06</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,02; 16,98</t>
+          <t>1,74; 16,52</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>69,09%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>39,2%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>44,08%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>65,5%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>31,34%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>26,07%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>69,09%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>39,2%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>21,98; 121,8</t>
+          <t>24,71; 126,14</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 79,61</t>
+          <t>-0,82; 87,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 71,84</t>
+          <t>1,72; 93,91</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25,33; 127,76</t>
+          <t>24,16; 122,11</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,19; 94,96</t>
+          <t>-1,1; 84,99</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 89,1</t>
+          <t>-10,97; 78,31</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,8; 111,53</t>
+          <t>36,86; 110,85</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>8,58; 70,15</t>
+          <t>7,55; 68,35</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3,16; 72,73</t>
+          <t>5,72; 70,39</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-13,6</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-9,65</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-24,4</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-11,76</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-5,33</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-21,52</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-13,6</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-9,65</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-23,78</t>
+          <t>-22,29</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-22,69</t>
+          <t>-23,39</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-22,96; -1,55</t>
+          <t>-22,6; -3,13</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 5,1</t>
+          <t>-19,72; -0,17</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-30,83; -11,1</t>
+          <t>-33,89; -15,92</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-23,94; -3,79</t>
+          <t>-21,54; -1,24</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 0,12</t>
+          <t>-15,51; 5,11</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-33,07; -14,76</t>
+          <t>-31,12; -12,26</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-20,55; -6,17</t>
+          <t>-19,84; -5,66</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-14,63; -0,33</t>
+          <t>-14,81; -0,91</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-28,96; -16,13</t>
+          <t>-30,03; -16,54</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-35,55%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-25,22%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-63,79%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-32,4%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-14,67%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-59,27%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-35,55%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-25,22%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-62,15%</t>
+          <t>-61,4%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-60,82%</t>
+          <t>-62,67%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-53,37; -1,14</t>
+          <t>-51,79; -9,35</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 18,09</t>
+          <t>-43,85; -0,3</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-73,39; -37,25</t>
+          <t>-76,91; -48,66</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-53,59; -11,45</t>
+          <t>-51,84; -3,53</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-44,0; 0,61</t>
+          <t>-36,46; 17,6</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-75,69; -43,65</t>
+          <t>-74,68; -41,62</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-49,56; -17,86</t>
+          <t>-47,8; -16,57</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-34,82; -0,38</t>
+          <t>-35,73; -2,65</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-70,71; -47,73</t>
+          <t>-72,05; -48,95</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>10,33</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>9,44</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-10,57</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>9,93</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>6,89</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-6,88</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>10,33</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>9,44</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-10,82</t>
+          <t>-9,72</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-8,99</t>
+          <t>-10,17</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>5,19; 15,21</t>
+          <t>5,53; 14,66</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,97; 11,23</t>
+          <t>4,85; 14,0</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 3,72</t>
+          <t>-14,77; -6,81</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5,91; 14,63</t>
+          <t>4,77; 15,16</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>5,17; 14,24</t>
+          <t>2,59; 11,98</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-14,75; -6,74</t>
+          <t>-14,13; -5,6</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,82; 13,54</t>
+          <t>6,89; 13,26</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>4,87; 11,43</t>
+          <t>5,0; 11,5</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-12,44; -3,56</t>
+          <t>-13,04; -7,14</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>36,97%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>33,78%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-37,83%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>35,34%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>24,53%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-24,48%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>36,97%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>33,78%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-38,75%</t>
+          <t>-34,6%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-32,08%</t>
+          <t>-36,3%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>17,01; 59,31</t>
+          <t>17,91; 57,26</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>6,6; 44,69</t>
+          <t>15,63; 55,17</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-41,18; 14,99</t>
+          <t>-48,51; -25,7</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>19,92; 57,51</t>
+          <t>15,67; 59,94</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>16,86; 55,33</t>
+          <t>7,85; 46,3</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-49,41; -26,73</t>
+          <t>-45,9; -20,91</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>23,0; 50,72</t>
+          <t>22,88; 49,8</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>16,82; 43,64</t>
+          <t>16,61; 43,42</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-42,03; -12,02</t>
+          <t>-44,25; -27,12</t>
         </is>
       </c>
     </row>
